--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487033_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487033_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1176</v>
+        <v>1.7373</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6627</v>
+        <v>3.8005</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5451</v>
+        <v>-2.0632</v>
       </c>
       <c r="G2" t="n">
         <v>-2.7674</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2778</v>
+        <v>-1.6581</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.805</v>
+        <v>-0.6672</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4727</v>
+        <v>-0.9909</v>
       </c>
       <c r="V2" t="n">
         <v>5.1977</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.745</v>
+        <v>0.0529</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2334</v>
+        <v>4.3712</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.4884</v>
+        <v>-4.3183</v>
       </c>
       <c r="G3" t="n">
         <v>2.7752</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4898</v>
+        <v>-1.1819</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9835</v>
+        <v>-0.8457</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4937</v>
+        <v>-0.3362</v>
       </c>
       <c r="V3" t="n">
         <v>-1.9264</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4878</v>
+        <v>-1.1804</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2443</v>
+        <v>-2.044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7565</v>
+        <v>0.8636</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3807</v>
@@ -766,13 +766,13 @@
         <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6861</v>
+        <v>-0.3787</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2829</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4032</v>
+        <v>-0.2961</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>A. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1527</v>
+        <v>-2.305</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2151</v>
+        <v>-0.0125</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9376</v>
+        <v>-2.2926</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3995</v>
+        <v>-1.4261</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6134</v>
+        <v>0.9688</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7861</v>
+        <v>-2.3948</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3371</v>
+        <v>0.3821</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2898</v>
+        <v>1.6766</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6269</v>
+        <v>-1.2945</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0624</v>
+        <v>-1.8082</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9032</v>
+        <v>-0.7079</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1592</v>
+        <v>-1.1003</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>0.347</v>
+        <v>-0.616</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4574</v>
+        <v>-0.3946</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1104</v>
+        <v>-0.2214</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2859</v>
+        <v>-1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GOMEZ FERNANDEZ</t>
+          <t>A. RUIZ VICENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3447</v>
+        <v>-2.4368</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2127</v>
+        <v>-1.0619</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1319</v>
+        <v>-1.3749</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4261</v>
+        <v>-2.8746</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9688</v>
+        <v>-1.5886</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3948</v>
+        <v>-1.286</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3821</v>
+        <v>-1.0261</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6766</v>
+        <v>-0.4399</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2945</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8082</v>
+        <v>-1.8484</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7079</v>
+        <v>-1.1487</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1003</v>
+        <v>-0.6998</v>
       </c>
       <c r="P6" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.8904</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5949</v>
+        <v>-0.2987</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0608</v>
+        <v>-0.5916</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.228</v>
+        <v>0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RUIZ VICENTE</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2359</v>
+        <v>-2.4957</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7004</v>
+        <v>-1.4778</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5355</v>
+        <v>-1.0179</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.8746</v>
+        <v>-2.3995</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5886</v>
+        <v>-1.6134</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.286</v>
+        <v>-0.7861</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0261</v>
+        <v>-0.3371</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4399</v>
+        <v>0.2898</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.6269</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8484</v>
+        <v>-2.0624</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1487</v>
+        <v>-1.9032</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6998</v>
+        <v>-0.1592</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6895</v>
+        <v>0.004</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9373</v>
+        <v>0.1947</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7522</v>
+        <v>-0.1907</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9421</v>
+        <v>0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>1.228</v>
+        <v>-0.3704</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.5639</v>
+        <v>-4.3181</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7198</v>
+        <v>-1.5007</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8442</v>
+        <v>-2.8174</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0333</v>
@@ -1078,13 +1078,13 @@
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8369</v>
+        <v>-1.591</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8791</v>
+        <v>-0.66</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9578</v>
+        <v>-0.9311</v>
       </c>
       <c r="V8" t="n">
         <v>0.2014</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6997</v>
+        <v>-4.4865</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3834</v>
+        <v>-2.4647</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3163</v>
+        <v>-2.0219</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8647</v>
@@ -1156,13 +1156,13 @@
         <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9122</v>
+        <v>-1.6991</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8196</v>
+        <v>-0.9009</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0926</v>
+        <v>-0.7982</v>
       </c>
       <c r="V9" t="n">
         <v>0.0422</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.6221</v>
+        <v>-15.4323</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5796</v>
+        <v>-0.3898999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-15.0425</v>
+        <v>-15.0426</v>
       </c>
       <c r="G10" t="n">
         <v>-9.9711</v>
@@ -1213,16 +1213,16 @@
         <v>14.0902</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.5796</v>
+        <v>-6.579599999999999</v>
       </c>
       <c r="M10" t="n">
         <v>-17.4815</v>
       </c>
       <c r="N10" t="n">
-        <v>-9.784500000000001</v>
+        <v>-9.7845</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.697299999999999</v>
+        <v>-7.6973</v>
       </c>
       <c r="P10" t="n">
         <v>-0.9650999999999996</v>
@@ -1234,13 +1234,13 @@
         <v>11.5805</v>
       </c>
       <c r="S10" t="n">
-        <v>-9.201000000000001</v>
+        <v>-8.011199999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.8449</v>
+        <v>-3.655</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.356</v>
+        <v>-4.356199999999999</v>
       </c>
       <c r="V10" t="n">
         <v>3.5149</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.4277</v>
+        <v>6.9681</v>
       </c>
       <c r="E11" t="n">
-        <v>7.1546</v>
+        <v>5.1054</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2732</v>
+        <v>1.8626</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>5.4508</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3987</v>
+        <v>-1.8215</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4987</v>
+        <v>7.2723</v>
       </c>
       <c r="J11" t="n">
-        <v>4.542</v>
+        <v>6.3517</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8315</v>
+        <v>-0.6728</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7104</v>
+        <v>7.0245</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.442</v>
+        <v>-0.9009</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2303</v>
+        <v>-1.1487</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7883</v>
+        <v>0.2478</v>
       </c>
       <c r="P11" t="n">
-        <v>0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.193</v>
+        <v>-2.3161</v>
       </c>
       <c r="R11" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6064</v>
+        <v>1.4244</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5197</v>
+        <v>0.784</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0866</v>
+        <v>0.6405</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2436</v>
+        <v>0.2859</v>
       </c>
       <c r="W11" t="n">
         <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.3945</v>
+        <v>5.8916</v>
       </c>
       <c r="E12" t="n">
-        <v>7.416</v>
+        <v>5.7526</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0215</v>
+        <v>0.139</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6418</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2116</v>
+        <v>-0.3987</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5698</v>
+        <v>3.4987</v>
       </c>
       <c r="J12" t="n">
-        <v>2.169</v>
+        <v>4.542</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5924</v>
+        <v>1.8315</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4234</v>
+        <v>2.7104</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5272</v>
+        <v>-1.442</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3808</v>
+        <v>-2.2303</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1464</v>
+        <v>0.7883</v>
       </c>
       <c r="P12" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3823</v>
+        <v>2.0702</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4702</v>
+        <v>1.1178</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.9525</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5983</v>
+        <v>-0.2436</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7418</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1435</v>
+        <v>-0.5295</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5516</v>
+        <v>5.6257</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3043</v>
+        <v>5.5133</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2472</v>
+        <v>0.1124</v>
       </c>
       <c r="G13" t="n">
-        <v>5.4508</v>
+        <v>1.6418</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8215</v>
+        <v>2.2116</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2723</v>
+        <v>-0.5698</v>
       </c>
       <c r="J13" t="n">
-        <v>6.3517</v>
+        <v>2.169</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6728</v>
+        <v>2.5924</v>
       </c>
       <c r="L13" t="n">
-        <v>7.0245</v>
+        <v>-0.4234</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9009</v>
+        <v>-0.5272</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1487</v>
+        <v>-0.3808</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2478</v>
+        <v>-0.1464</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3161</v>
+        <v>-0.965</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.6135</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0172</v>
+        <v>1.5676</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0251</v>
+        <v>0.0459</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2859</v>
+        <v>1.5983</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2859</v>
+        <v>2.7418</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.1435</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4504</v>
+        <v>2.2094</v>
       </c>
       <c r="E14" t="n">
         <v>4.3752</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9249</v>
+        <v>-2.1658</v>
       </c>
       <c r="G14" t="n">
         <v>3.8174</v>
@@ -1546,13 +1546,13 @@
         <v>0.965</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9538</v>
+        <v>0.7129</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0462</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0.7591</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1278</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.744</v>
+        <v>0.6776</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5591</v>
+        <v>0.3588</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1849</v>
+        <v>0.3188</v>
       </c>
       <c r="G15" t="n">
         <v>0.2251</v>
@@ -1624,13 +1624,13 @@
         <v>0.386</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1329</v>
+        <v>0.0664</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1468</v>
+        <v>-0.0535</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0139</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6229</v>
+        <v>0.5758</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3944</v>
+        <v>0.3813</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7715</v>
+        <v>0.1945</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0464</v>
+        <v>2.0539</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3434</v>
+        <v>0.146</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3898</v>
+        <v>1.9079</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3071</v>
+        <v>2.728</v>
       </c>
       <c r="K16" t="n">
-        <v>0.119</v>
+        <v>0.8073</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1881</v>
+        <v>1.9207</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2607</v>
+        <v>-0.6741</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4624</v>
+        <v>-0.6612</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2017</v>
+        <v>-0.0129</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3161</v>
       </c>
       <c r="R16" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4184</v>
+        <v>0.9502</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0873</v>
+        <v>0.3398</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3311</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.228</v>
+        <v>-1.2702</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.228</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5292</v>
+        <v>0.5758</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0314</v>
+        <v>-0.9313</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5606</v>
+        <v>1.5071</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6704</v>
@@ -1780,13 +1780,13 @@
         <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1573</v>
+        <v>0.2039</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2683</v>
+        <v>-0.1682</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4257</v>
+        <v>0.3721</v>
       </c>
       <c r="V17" t="n">
         <v>0.6562</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5226</v>
+        <v>0.4494</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3813</v>
+        <v>1.1941</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1413</v>
+        <v>-0.7447</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0539</v>
+        <v>1.0464</v>
       </c>
       <c r="H18" t="n">
-        <v>0.146</v>
+        <v>-1.3434</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9079</v>
+        <v>2.3898</v>
       </c>
       <c r="J18" t="n">
-        <v>2.728</v>
+        <v>1.3071</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8073</v>
+        <v>0.119</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9207</v>
+        <v>1.1881</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6741</v>
+        <v>-0.2607</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6612</v>
+        <v>-1.4624</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0129</v>
+        <v>1.2017</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3161</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>0.897</v>
+        <v>0.2449</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3398</v>
+        <v>-0.113</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5572</v>
+        <v>0.3579</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2702</v>
+        <v>-1.228</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8999</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3448</v>
+        <v>-0.4728</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1732</v>
+        <v>-1.9002</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8284</v>
+        <v>1.4274</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1345</v>
+        <v>-3.0035</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9489</v>
+        <v>-0.2225</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1856</v>
+        <v>-2.7811</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5334</v>
+        <v>-2.1026</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2795</v>
+        <v>0.9262</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2538</v>
+        <v>-3.0288</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6012</v>
+        <v>-0.9009</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6694</v>
+        <v>-1.1487</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0682</v>
+        <v>0.2478</v>
       </c>
       <c r="P19" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.193</v>
+        <v>-2.1231</v>
       </c>
       <c r="R19" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2525</v>
+        <v>1.4958</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4468</v>
+        <v>0.4835</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1943</v>
+        <v>1.0123</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6562</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. DIEZ TIDALA</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.569</v>
+        <v>-1.0444</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5172</v>
+        <v>-1.8728</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0518</v>
+        <v>0.8284</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7731</v>
+        <v>-2.1345</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3726</v>
+        <v>-1.9489</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4006</v>
+        <v>-0.1856</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6262</v>
+        <v>-1.5334</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0414</v>
+        <v>-0.2795</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6676</v>
+        <v>-1.2538</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1469</v>
+        <v>-0.6012</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.414</v>
+        <v>-1.6694</v>
       </c>
       <c r="O20" t="n">
-        <v>0.267</v>
+        <v>1.0682</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R20" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0238</v>
+        <v>0.0479</v>
       </c>
       <c r="T20" t="n">
-        <v>0.074</v>
+        <v>-0.1464</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0978</v>
+        <v>0.1943</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>L. DIEZ TIDALA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7207</v>
+        <v>-1.2818</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.202</v>
+        <v>-1.4171</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4813</v>
+        <v>0.1353</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0035</v>
+        <v>-0.7731</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2225</v>
+        <v>-0.3726</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7811</v>
+        <v>-0.4006</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1026</v>
+        <v>-0.6262</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9262</v>
+        <v>0.0414</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.0288</v>
+        <v>-0.6676</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9009</v>
+        <v>-0.1469</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1487</v>
+        <v>-0.414</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2478</v>
+        <v>0.267</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2479</v>
+        <v>0.2634</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8183</v>
+        <v>0.1742</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0661</v>
+        <v>0.0892</v>
       </c>
       <c r="V21" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9863</v>
+        <v>-2.8847</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6186</v>
+        <v>-1.517</v>
       </c>
       <c r="F22" t="n">
         <v>-1.3677</v>
@@ -2170,10 +2170,10 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3265</v>
+        <v>0.775</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6848</v>
+        <v>0.4168</v>
       </c>
       <c r="U22" t="n">
         <v>0.3582</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>16.6221</v>
+        <v>17.2897</v>
       </c>
       <c r="E23" t="n">
-        <v>15.0425</v>
+        <v>15.0423</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5795</v>
+        <v>2.2473</v>
       </c>
       <c r="G23" t="n">
-        <v>9.971100000000002</v>
+        <v>9.971100000000005</v>
       </c>
       <c r="H23" t="n">
         <v>-4.3059</v>
@@ -2227,7 +2227,7 @@
         <v>9.784599999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>7.6972</v>
+        <v>7.697199999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-7.5106</v>
@@ -2248,13 +2248,13 @@
         <v>12.5454</v>
       </c>
       <c r="S23" t="n">
-        <v>9.201100000000002</v>
+        <v>9.868500000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>4.356200000000001</v>
+        <v>4.3564</v>
       </c>
       <c r="U23" t="n">
-        <v>4.8447</v>
+        <v>5.5124</v>
       </c>
       <c r="V23" t="n">
         <v>-3.5149</v>
